--- a/artfynd/A 12745-2024 artfynd.xlsx
+++ b/artfynd/A 12745-2024 artfynd.xlsx
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566960</v>
+        <v>117566981</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451892</v>
+        <v>451943</v>
       </c>
       <c r="R9" t="n">
-        <v>6991949</v>
+        <v>6991895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117566981</v>
+        <v>117566960</v>
       </c>
       <c r="B10" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451943</v>
+        <v>451892</v>
       </c>
       <c r="R10" t="n">
-        <v>6991895</v>
+        <v>6991949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 12745-2024 artfynd.xlsx
+++ b/artfynd/A 12745-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117566958</v>
+        <v>117566982</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451614</v>
+        <v>451965</v>
       </c>
       <c r="R2" t="n">
-        <v>6991948</v>
+        <v>6991897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117566962</v>
+        <v>117566958</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451907</v>
+        <v>451614</v>
       </c>
       <c r="R3" t="n">
-        <v>6991907</v>
+        <v>6991948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117566963</v>
+        <v>117566980</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451994</v>
+        <v>451851</v>
       </c>
       <c r="R4" t="n">
-        <v>6991857</v>
+        <v>6991952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117566961</v>
+        <v>117566960</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451819</v>
+        <v>451892</v>
       </c>
       <c r="R5" t="n">
-        <v>6991952</v>
+        <v>6991949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117566982</v>
+        <v>117566961</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451965</v>
+        <v>451819</v>
       </c>
       <c r="R7" t="n">
-        <v>6991897</v>
+        <v>6991952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117566980</v>
+        <v>117566981</v>
       </c>
       <c r="B8" t="n">
         <v>79561</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451851</v>
+        <v>451943</v>
       </c>
       <c r="R8" t="n">
-        <v>6991952</v>
+        <v>6991895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566981</v>
+        <v>117566963</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451943</v>
+        <v>451994</v>
       </c>
       <c r="R9" t="n">
-        <v>6991895</v>
+        <v>6991857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117566960</v>
+        <v>117566962</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451892</v>
+        <v>451907</v>
       </c>
       <c r="R10" t="n">
-        <v>6991949</v>
+        <v>6991907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 12745-2024 artfynd.xlsx
+++ b/artfynd/A 12745-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117566982</v>
+        <v>117566963</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451965</v>
+        <v>451994</v>
       </c>
       <c r="R2" t="n">
-        <v>6991897</v>
+        <v>6991857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117566958</v>
+        <v>117566962</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451614</v>
+        <v>451907</v>
       </c>
       <c r="R3" t="n">
-        <v>6991948</v>
+        <v>6991907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117566980</v>
+        <v>117566959</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451851</v>
+        <v>451794</v>
       </c>
       <c r="R4" t="n">
-        <v>6991952</v>
+        <v>6992055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117566960</v>
+        <v>117566980</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451892</v>
+        <v>451851</v>
       </c>
       <c r="R5" t="n">
-        <v>6991949</v>
+        <v>6991952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117566959</v>
+        <v>117566982</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451794</v>
+        <v>451965</v>
       </c>
       <c r="R6" t="n">
-        <v>6992055</v>
+        <v>6991897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1203,7 @@
         <v>117566961</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117566981</v>
+        <v>117566960</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451943</v>
+        <v>451892</v>
       </c>
       <c r="R8" t="n">
-        <v>6991895</v>
+        <v>6991949</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117566963</v>
+        <v>117566958</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451994</v>
+        <v>451614</v>
       </c>
       <c r="R9" t="n">
-        <v>6991857</v>
+        <v>6991948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117566962</v>
+        <v>117566981</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451907</v>
+        <v>451943</v>
       </c>
       <c r="R10" t="n">
-        <v>6991907</v>
+        <v>6991895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
